--- a/server/uploads/1778234793152-hotel_rates_expanded.xlsx
+++ b/server/uploads/1778234793152-hotel_rates_expanded.xlsx
@@ -464,7 +464,7 @@
         <v>TBO Holidays</v>
       </c>
       <c r="C2" t="str">
-        <v>The Leela Palace New Delhi</v>
+        <v>The Leela Palace New Delhii</v>
       </c>
       <c r="D2" t="str">
         <v>India</v>
@@ -487,14 +487,14 @@
       <c r="J2" t="str">
         <v>CP</v>
       </c>
-      <c r="K2">
-        <v>18500</v>
-      </c>
-      <c r="L2">
-        <v>6500</v>
-      </c>
-      <c r="M2">
-        <v>4200</v>
+      <c r="K2" t="str">
+        <v>1500</v>
+      </c>
+      <c r="L2" t="str">
+        <v>1200</v>
+      </c>
+      <c r="M2" t="str">
+        <v>1300</v>
       </c>
       <c r="N2" t="str">
         <v>INR</v>
@@ -509,7 +509,7 @@
         <v>Deluxe | CP | The Leela Palace New Delhi Hotel | Wifi | Air Conditioning | Daily Housekeeping | Concierge | Room Service</v>
       </c>
       <c r="R2" t="str">
-        <v>29100</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3">
@@ -1572,8 +1572,8 @@
       <c r="Q21" t="str">
         <v>Towers Exclusive | MAP | ITC Royal Bengal Hotel | Wifi | Air Conditioning | Daily Housekeeping | Lounge Access | Parking</v>
       </c>
-      <c r="R21">
-        <v>21200</v>
+      <c r="R21" t="str">
+        <v>200</v>
       </c>
     </row>
     <row r="22">
